--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488105_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488105_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6644</v>
+        <v>11.6354</v>
       </c>
       <c r="E2" t="n">
-        <v>8.334300000000001</v>
+        <v>8.193</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3301</v>
+        <v>3.4424</v>
       </c>
       <c r="G2" t="n">
         <v>4.5051</v>
@@ -610,13 +610,13 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>0.754</v>
+        <v>0.725</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3196</v>
+        <v>0.1782</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4344</v>
+        <v>0.5468</v>
       </c>
       <c r="V2" t="n">
         <v>4.2249</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5018</v>
+        <v>3.9736</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1323</v>
+        <v>3.0533</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3695</v>
+        <v>0.9202</v>
       </c>
       <c r="G3" t="n">
         <v>2.6819</v>
@@ -688,13 +688,13 @@
         <v>1.3876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6988</v>
+        <v>0.1706</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0148</v>
+        <v>-0.0641</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.2348</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2666</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7174</v>
+        <v>3.9046</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9782</v>
+        <v>3.1654</v>
       </c>
       <c r="F4" t="n">
         <v>0.7392</v>
@@ -766,10 +766,10 @@
         <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1872</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.121</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U4" t="n">
         <v>-0.06619999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.607</v>
+        <v>3.8232</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7673</v>
+        <v>4.0959</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1604</v>
+        <v>-0.2727</v>
       </c>
       <c r="G5" t="n">
         <v>0.552</v>
@@ -844,13 +844,13 @@
         <v>1.1893</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5198</v>
+        <v>0.736</v>
       </c>
       <c r="T5" t="n">
-        <v>0.213</v>
+        <v>0.5416</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3067</v>
+        <v>0.1944</v>
       </c>
       <c r="V5" t="n">
         <v>1.5441</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>P. IBANEZ FIDALGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4796</v>
+        <v>2.2466</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2681</v>
+        <v>1.3849</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2114</v>
+        <v>0.8617</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3286</v>
+        <v>2.4337</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.031</v>
+        <v>0.8056</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3596</v>
+        <v>1.6281</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6901</v>
+        <v>1.5275</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.528</v>
+        <v>0.0409</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2181</v>
+        <v>1.4866</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6385</v>
+        <v>0.9062</v>
       </c>
       <c r="N6" t="n">
-        <v>0.497</v>
+        <v>0.7647</v>
       </c>
       <c r="O6" t="n">
         <v>0.1415</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5652</v>
+        <v>0.1588</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5692</v>
+        <v>0.0488</v>
       </c>
       <c r="U6" t="n">
-        <v>0.996</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2071</v>
+        <v>-0.9405</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2071</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2891</v>
+        <v>1.7476</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0145</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3761</v>
+        <v>1.7622</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5397999999999999</v>
+        <v>1.3286</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2534</v>
+        <v>-2.031</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7136</v>
+        <v>3.3596</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5149</v>
+        <v>0.6901</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4306</v>
+        <v>-2.528</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0842</v>
+        <v>3.2181</v>
       </c>
       <c r="M7" t="n">
-        <v>0.025</v>
+        <v>0.6385</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8228</v>
+        <v>0.497</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.1415</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>0.551</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3892</v>
+        <v>0.2865</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1618</v>
+        <v>0.5468</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. IBANEZ FIDALGO</t>
+          <t>S. CASTRO BRAVO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2465</v>
+        <v>1.5175</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6371</v>
+        <v>0.6475</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4337</v>
+        <v>1.072</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8056</v>
+        <v>1.7052</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6281</v>
+        <v>-0.6333</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5275</v>
+        <v>0.713</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0409</v>
+        <v>1.3519</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4866</v>
+        <v>-0.639</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9062</v>
+        <v>0.359</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7647</v>
+        <v>0.3533</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1415</v>
+        <v>0.0057</v>
       </c>
       <c r="P8" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.1982</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.5947</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-0.9911</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.5858</v>
-      </c>
       <c r="S8" t="n">
-        <v>-0.8414</v>
+        <v>0.3157</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7267</v>
+        <v>0.3553</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1147</v>
+        <v>-0.0396</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9405</v>
+        <v>-0.2666</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7403</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0252</v>
+        <v>1.1437</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6125</v>
+        <v>-0.5501</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6377</v>
+        <v>1.6938</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7665</v>
@@ -1156,13 +1156,13 @@
         <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5073</v>
+        <v>0.6259</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0883</v>
+        <v>0.1506</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4191</v>
+        <v>0.4752</v>
       </c>
       <c r="V9" t="n">
         <v>2.0772</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. ALVAREZ ALVAREZ</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7827</v>
+        <v>1.1134</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0353</v>
+        <v>-0.2908</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7474</v>
+        <v>1.4042</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9169</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2003</v>
+        <v>1.2534</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1172</v>
+        <v>-0.7136</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6549</v>
+        <v>0.5149</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0605</v>
+        <v>0.4306</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7154</v>
+        <v>0.0842</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.262</v>
+        <v>0.025</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1398</v>
+        <v>0.8228</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4018</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P10" t="n">
         <v>0.1982</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8274</v>
+        <v>0.3753</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8884</v>
+        <v>0.1855</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0609</v>
+        <v>0.1899</v>
       </c>
       <c r="V10" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. CASTRO BRAVO</t>
+          <t>N. ALVAREZ ALVAREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6369</v>
+        <v>0.6913</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2982</v>
+        <v>-0.1685</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3387</v>
+        <v>0.8597</v>
       </c>
       <c r="G11" t="n">
-        <v>1.072</v>
+        <v>-0.9169</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7052</v>
+        <v>0.2003</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6333</v>
+        <v>-1.1172</v>
       </c>
       <c r="J11" t="n">
-        <v>0.713</v>
+        <v>-0.6549</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3519</v>
+        <v>0.0605</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.639</v>
+        <v>-0.7154</v>
       </c>
       <c r="M11" t="n">
-        <v>0.359</v>
+        <v>-0.262</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3533</v>
+        <v>0.1398</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0057</v>
+        <v>-0.4018</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.1982</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5649</v>
+        <v>0.736</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2165</v>
+        <v>0.6846</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3484</v>
+        <v>0.0514</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2666</v>
+        <v>0.674</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2666</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="12">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2017</v>
+        <v>0.1207</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4512</v>
+        <v>0.1456</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2495</v>
+        <v>-0.0249</v>
       </c>
       <c r="G14" t="n">
         <v>0.9395</v>
@@ -1546,13 +1546,13 @@
         <v>0.3964</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1939</v>
+        <v>0.1129</v>
       </c>
       <c r="T14" t="n">
-        <v>0.18</v>
+        <v>-0.1257</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0139</v>
+        <v>0.2386</v>
       </c>
       <c r="V14" t="n">
         <v>-0.337</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7471</v>
+        <v>-0.5766</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.3434</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.177</v>
+        <v>-0.2331</v>
       </c>
       <c r="G15" t="n">
         <v>0.2191</v>
@@ -1624,13 +1624,13 @@
         <v>0.5947</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6196</v>
+        <v>0.7901</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2754</v>
+        <v>0.5021</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3442</v>
+        <v>0.288</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>31.3132</v>
+        <v>32.249</v>
       </c>
       <c r="E16" t="n">
-        <v>19.5127</v>
+        <v>20.4488</v>
       </c>
       <c r="F16" t="n">
-        <v>11.8003</v>
+        <v>11.8002</v>
       </c>
       <c r="G16" t="n">
         <v>14.4009</v>
@@ -1678,13 +1678,13 @@
         <v>14.7699</v>
       </c>
       <c r="K16" t="n">
-        <v>8.942399999999999</v>
+        <v>8.942400000000001</v>
       </c>
       <c r="L16" t="n">
         <v>5.827099999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3688000000000001</v>
+        <v>-0.3688000000000002</v>
       </c>
       <c r="N16" t="n">
         <v>2.9129</v>
@@ -1702,16 +1702,16 @@
         <v>13.8756</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6435</v>
+        <v>5.579499999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8737</v>
+        <v>2.8096</v>
       </c>
       <c r="U16" t="n">
-        <v>2.7699</v>
+        <v>2.7701</v>
       </c>
       <c r="V16" t="n">
-        <v>7.3131</v>
+        <v>7.313100000000001</v>
       </c>
       <c r="W16" t="n">
         <v>11.7894</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1706</v>
+        <v>1.3294</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7065</v>
+        <v>1.827</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8771</v>
+        <v>-0.4977</v>
       </c>
       <c r="G17" t="n">
         <v>1.2592</v>
@@ -1780,13 +1780,13 @@
         <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7221</v>
+        <v>-0.2221</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.6847</v>
+        <v>-0.5642</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0373</v>
+        <v>0.3421</v>
       </c>
       <c r="V17" t="n">
         <v>1.8781</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2411</v>
+        <v>-0.2313</v>
       </c>
       <c r="E18" t="n">
         <v>4.8853</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.1264</v>
+        <v>-5.1166</v>
       </c>
       <c r="G18" t="n">
         <v>2.4196</v>
@@ -1858,13 +1858,13 @@
         <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0364</v>
+        <v>-0.0266</v>
       </c>
       <c r="T18" t="n">
         <v>-0.6385</v>
       </c>
       <c r="U18" t="n">
-        <v>0.602</v>
+        <v>0.6118</v>
       </c>
       <c r="V18" t="n">
         <v>-3.0208</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4858</v>
+        <v>-1.1123</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2092</v>
+        <v>-0.1074</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2766</v>
+        <v>-1.005</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2876</v>
@@ -1936,13 +1936,13 @@
         <v>0.1982</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7929</v>
+        <v>-0.4194</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2496</v>
+        <v>-0.1477</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5433</v>
+        <v>-0.2717</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6036</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. PERERIRA</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9642</v>
+        <v>-2.6749</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1824</v>
+        <v>-2.1124</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7818</v>
+        <v>-0.5625</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2825</v>
+        <v>-1.9954</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4291</v>
+        <v>-0.3499</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-1.6455</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1207</v>
+        <v>-0.1612</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0404</v>
+        <v>0.4376</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0804</v>
+        <v>-0.5988</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4032</v>
+        <v>-1.8342</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4695</v>
+        <v>-0.7875</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9337</v>
+        <v>-1.0467</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.312</v>
+        <v>-0.2861</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2933</v>
+        <v>0.2816</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8701</v>
+        <v>-0.8731</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8701</v>
+        <v>-0.1992</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. DAVID ROCHA</t>
+          <t>T. PERERIRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.153</v>
+        <v>-2.9923</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0627</v>
+        <v>-1.1824</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0902</v>
+        <v>-1.8099</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.8331</v>
+        <v>-1.2825</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.0059</v>
+        <v>-0.4291</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8272</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.6556</v>
+        <v>0.1207</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.0167</v>
+        <v>0.0404</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.639</v>
+        <v>0.0804</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1775</v>
+        <v>-1.4032</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9893</v>
+        <v>-0.4695</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1882</v>
+        <v>-0.9337</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.0468</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1103</v>
+        <v>-0.312</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0417</v>
+        <v>0.2652</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6115</v>
+        <v>-0.8701</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1378</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5718</v>
+        <v>-3.133</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2043</v>
+        <v>-2.5099</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3676</v>
+        <v>-0.6231</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0953</v>
@@ -2248,13 +2248,13 @@
         <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5976</v>
+        <v>-0.1588</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0769</v>
+        <v>-0.3825</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5207000000000001</v>
+        <v>0.2237</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4737</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>D. DAVID ROCHA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7426</v>
+        <v>-3.1693</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5199</v>
+        <v>-2.2665</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2226</v>
+        <v>-0.9028</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9954</v>
+        <v>-4.8331</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3499</v>
+        <v>-3.0059</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6455</v>
+        <v>-1.8272</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1612</v>
+        <v>-2.6556</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4376</v>
+        <v>-2.0167</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5988</v>
+        <v>-0.639</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8342</v>
+        <v>-2.1775</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7875</v>
+        <v>-0.9893</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0467</v>
+        <v>-1.1882</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0722</v>
+        <v>0.0523</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6936</v>
+        <v>-0.0934</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3786</v>
+        <v>0.1457</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8731</v>
+        <v>1.6115</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.674</v>
+        <v>1.4737</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1992</v>
+        <v>0.1378</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1686</v>
+        <v>-3.1852</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7121</v>
+        <v>-2.3046</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4565</v>
+        <v>-0.8806</v>
       </c>
       <c r="G25" t="n">
         <v>-1.0203</v>
@@ -2404,13 +2404,13 @@
         <v>0.9911</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3376</v>
+        <v>-0.3542</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8736</v>
+        <v>-0.4661</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4641</v>
+        <v>0.1119</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8107</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.2059</v>
+        <v>-11.139</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.765</v>
+        <v>-7.2931</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.4408</v>
+        <v>-3.8459</v>
       </c>
       <c r="G26" t="n">
         <v>-6.8371</v>
@@ -2482,13 +2482,13 @@
         <v>0.7929</v>
       </c>
       <c r="S26" t="n">
-        <v>1.0635</v>
+        <v>0.1304</v>
       </c>
       <c r="T26" t="n">
-        <v>1.7109</v>
+        <v>0.1829</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6474</v>
+        <v>-0.0525</v>
       </c>
       <c r="V26" t="n">
         <v>-0.2696</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-31.313</v>
+        <v>-27.9173</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.8002</v>
+        <v>-11.8004</v>
       </c>
       <c r="F27" t="n">
-        <v>-19.5127</v>
+        <v>-16.1172</v>
       </c>
       <c r="G27" t="n">
         <v>-14.4008</v>
@@ -2533,7 +2533,7 @@
         <v>-2.545400000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3689999999999989</v>
+        <v>0.3689999999999998</v>
       </c>
       <c r="K27" t="n">
         <v>-2.912700000000001</v>
@@ -2560,13 +2560,13 @@
         <v>8.92</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.643600000000001</v>
+        <v>-1.248</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.7701</v>
+        <v>-2.77</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.8736</v>
+        <v>1.522</v>
       </c>
       <c r="V27" t="n">
         <v>-7.313099999999999</v>
